--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0226.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0226.xlsx
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Một đội máy bay không người lái hỗ trợ Rover trong chiến đấu.</t>
+          <t>Một đội máy bay không người lái hỗ trợ Vận Mệnh Giả trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Khi rời khỏi &lt;color=Highlight&gt;&lt;te href=851104&gt;Boost - Namipon Aid&lt;/te&gt;&lt;/color&gt;, tất cả Cộng Hưởng Giả trong đội sẽ được hồi phục HP.</t>
+          <t>Khi rời khỏi &lt;color=Highlight&gt;&lt;te href=851104&gt;Tăng Cường - Namipon Hỗ Trợ&lt;/te&gt;&lt;/color&gt;, tất cả Resonator trong đội sẽ được hồi phục HP.</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;&lt;te href=851106&gt;Combo - Hỗ Trợ Missile: Enhanced&lt;/te&gt;&lt;/color&gt; giờ bắn nhiều tên lửa hơn mỗi lần.</t>
+          <t>&lt;color=Highlight&gt;&lt;te href=851106&gt;Combo - Support Missile: Enhanced&lt;/te&gt;&lt;/color&gt; giờ bắn nhiều tên lửa hơn mỗi lần.</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Khi kích hoạt &lt;color=Highlight&gt;&lt;te href=851114&gt;Boost - Coffee's Shelter&lt;/te&gt;&lt;/color&gt;, sẽ nhận Khiên.</t>
+          <t>Khi kích hoạt &lt;color=Highlight&gt;&lt;te href=851114&gt;Tăng Cường - Nơi Trú Ẩn Của Cà Phê&lt;/te&gt;&lt;/color&gt;, sẽ nhận Khiên.</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả nhận một Lớp Khiên mỗi 20 giây.</t>
+          <t>Resonator nhận một Lớp Khiên mỗi 20 giây.</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>&lt;color=#fc6464&gt;Not Activated&lt;/color&gt;</t>
+          <t>&lt;color=#fc6464&gt;Chưa Kích Hoạt&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>&lt;color=#32dbb1&gt;Activated&lt;/color&gt;</t>
+          <t>&lt;color=#32dbb1&gt;Đã kích hoạt&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>&lt;color=#fffcf1&gt;{0}&lt;/color&gt;/&lt;color=#c2c2c2&gt;{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>&lt;color=#ffedae&gt;{0}&lt;/color&gt;/&lt;color=#ffffff&gt;{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>{0}m</t>
+          <t>{0}phút</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10585,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Sau khi kích hoạt Ram Dynamics, Cộng Hưởng Giả trong đội sẽ tăng Tỷ Lệ Tích Lũy Lệch Tần 5% trong 30 giây.</t>
+          <t>Sau khi kích hoạt Ram Dynamics, Resonator trong đội sẽ tăng Tỷ Lệ Tích Lũy Lệch Tần 5% trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Sau khi giải phóng Ram Dynamics, Tốc Độ Tích Lũy Lệch Nhịp của các Cộng Hưởng Giả trong đội tăng 10% trong 30 giây.</t>
+          <t>Sau khi giải phóng Ram Dynamics, Tốc Độ Tích Lũy Lệch Nhịp của các Resonator trong đội tăng 10% trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -10715,7 +10715,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Sau khi giải phóng Ram Dynamics, Tốc Độ Tích Lũy Lệch Nhịp của các Cộng Hưởng Giả trong đội tăng 15% trong 30 giây.</t>
+          <t>Sau khi giải phóng Ram Dynamics, Tốc Độ Tích Lũy Lệch Nhịp của các Resonator trong đội tăng 15% trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Sau khi giải phóng Ram Dynamics, các Cộng Hưởng Giả trong đội nhận được Khiên tương đương 100% Lực Trường của xe máy trong 30 giây.</t>
+          <t>Sau khi giải phóng Ram Dynamics, các Resonator trong đội nhận được Khiên tương đương 100% Lực Trường của xe máy trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Bão Hư Không, Cộng Hưởng Giả trong đội có Tốc Độ Tích Lũy Lệch Tần tăng thêm 10%.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội có Tốc Độ Tích Lũy Lệch Tần tăng thêm 10%.</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Bão Hư Không, Cộng Hưởng Giả trong đội có Tốc Độ Tích Lũy Lệch Tần tăng thêm 20%.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội có Tốc Độ Tích Lũy Lệch Tần tăng thêm 20%.</t>
         </is>
       </c>
     </row>
@@ -11040,7 +11040,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Bạn không sở hữu Cộng Hưởng Giả nào thuộc khu vực này.</t>
+          <t>Bạn không sở hữu Resonator nào thuộc khu vực này.</t>
         </is>
       </c>
     </row>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Vũ khí này đã được một Cộng Hưởng Giả khác sử dụng và có sẵn hồ sơ thử thách.</t>
+          <t>Vũ khí này đã được một Resonator khác sử dụng và có sẵn hồ sơ thử thách.</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Hồi Âm này đã được Cộng Hưởng Giả khác sử dụng và có sẵn dữ liệu thử thách.</t>
+          <t>Hồi Âm này đã được Resonator khác sử dụng và có sẵn dữ liệu thử thách.</t>
         </is>
       </c>
     </row>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả này đã có trong đội rồi. Cậu muốn thay thế bằng một Cộng Hưởng Giả Demo không?</t>
+          <t>Resonator này đã có trong đội rồi. Cậu muốn thay thế bằng một Resonator Demo không?</t>
         </is>
       </c>
     </row>
@@ -12277,7 +12277,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Một hoặc nhiều Cộng Hưởng Giả trong đội hình hiện tại không đủ Sinh Lực.</t>
+          <t>Một hoặc nhiều Resonator trong đội hình hiện tại không đủ Sinh Lực.</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>&lt;color=#94ffec&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -12732,7 +12732,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>&lt;color=#fc6464&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>&lt;color=#32dbb1&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -13772,7 +13772,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Thu thập 5.000 điểm với một đội duy nhất trong bất kỳ Giai Đoạn Thử Thách Kỳ Dị nào của Thử Thách Định Kỳ: Ma Trận Trạng Thái Cuối</t>
+          <t>Thu thập 5.000 điểm với một đội duy nhất trong bất kỳ Giai Đoạn Thử Thách Kỳ Dị nào của Thử Thách Định Kỳ: Endstate Matrix</t>
         </is>
       </c>
     </row>
@@ -13902,7 +13902,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Thu thập 20.000 điểm với một đội duy nhất ở bất kỳ Giai Đoạn Thử Thách nào của Mở Rộng Điểm Kỳ Dị trong Thử Thách Định Kỳ: Ma Trận Tận Thế</t>
+          <t>Thu thập 20.000 điểm với một đội duy nhất ở bất kỳ Giai Đoạn Thử Thách nào của Mở Rộng Điểm Kỳ Dị trong Thử Thách Định Kỳ: Endstate Matrix</t>
         </is>
       </c>
     </row>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Đạt tổng 100.000 điểm ở bất kỳ Giai Đoạn Thử Thách Mở Rộng Điểm Kỳ Dị nào trong Thử Thách Định Kỳ: Ma Trận Tận Thế</t>
+          <t>Đạt tổng 100.000 điểm ở bất kỳ Giai Đoạn Thử Thách Mở Rộng Điểm Kỳ Dị nào trong Thử Thách Định Kỳ: Endstate Matrix</t>
         </is>
       </c>
     </row>
@@ -14617,7 +14617,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Hoàn thành Bản Hologram Đồng Bộ: Dreamless I</t>
+          <t>Hoàn thành Bản Hologram Đồng Bộ: Synchronization - Dreamless I.</t>
         </is>
       </c>
     </row>
@@ -14682,7 +14682,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Hoàn thành Bản Hologram Đồng Bộ: Dreamless VI</t>
+          <t>Hoàn thành Bản Hologram Đồng Bộ: Synchronization - Dreamless VI.</t>
         </is>
       </c>
     </row>
@@ -16372,7 +16372,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>&lt;color=#32dbb1&gt;Activated&lt;/color&gt;</t>
+          <t>&lt;color=#32dbb1&gt;Đã kích hoạt&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>&lt;color=#32dbb1&gt;Activated&lt;/color&gt;</t>
+          <t>&lt;color=#32dbb1&gt;Đã kích hoạt&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16632,7 +16632,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>&lt;color=#32dbb1&gt;Activated&lt;/color&gt;</t>
+          <t>&lt;color=#32dbb1&gt;Đã kích hoạt&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Nhìn đây này! Ta muốn thấy cái vẻ ghen tị méo mó trên mặt ngươi!</t>
+          <t>Nhìn đây này! Tao muốn thấy cái vẻ ghen tị méo mó trên mặt mày!</t>
         </is>
       </c>
     </row>
@@ -20207,7 +20207,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Remaining: {0}</t>
+          <t>Còn lại: {0}</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Sau khi giải phóng Ram Dynamics, các Cộng Hưởng Giả trong đội có Tốc Độ Tích Lũy Lệch Nhịp cao hơn.</t>
+          <t>Sau khi giải phóng Ram Dynamics, các Resonator trong đội có Tốc Độ Tích Lũy Lệch Nhịp cao hơn.</t>
         </is>
       </c>
     </row>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Sau khi giải phóng Ram Dynamics, các Cộng Hưởng Giả trong đội nhận được Khiên.</t>
+          <t>Sau khi giải phóng Ram Dynamics, các Resonator trong đội nhận được Khiên.</t>
         </is>
       </c>
     </row>
@@ -20597,7 +20597,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Bão Hư Không, Cộng Hưởng Giả trong đội có Tốc Độ Tích Lũy Lệch Tần cao hơn.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội có Tốc Độ Tích Lũy Lệch Tần cao hơn.</t>
         </is>
       </c>
     </row>
@@ -21962,7 +21962,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Round {0}</t>
+          <t>Vòng {0}</t>
         </is>
       </c>
     </row>
@@ -28852,7 +28852,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Vũ khí và Echo đã được Cộng Hưởng Giả khác sử dụng trong thử thách.</t>
+          <t>Vũ khí và Echo đã được Resonator khác sử dụng trong thử thách.</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Khi Zahira mang những đỉnh cao danh vọng từ Học Viện về cho bộ tộc Roya, cô chưa từng nghĩ rằng chúng sẽ lan truyền khắp Rừng Bjartr như ngọn lửa hoang dã.</t>
+          <t>Khi Zahira mang những đỉnh cao danh vọng từ Học Viện về cho bộ tộc Roya, cô chưa từng nghĩ rằng chúng sẽ lan truyền khắp Bjartr Woods như ngọn lửa hoang dã.</t>
         </is>
       </c>
     </row>
@@ -30022,7 +30022,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem gợi ý.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem gợi ý.</t>
         </is>
       </c>
     </row>
